--- a/station.xlsx
+++ b/station.xlsx
@@ -1509,7 +1509,11 @@
       <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>تم تغير انفرتر قديم بواسطه م.رأفت بتاريخ13/1/2026</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
